--- a/KatalonData/RADTestData/JointFilerSSNmoreThan9Error.xlsx
+++ b/KatalonData/RADTestData/JointFilerSSNmoreThan9Error.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="67">
   <si>
     <t>Result</t>
   </si>
@@ -228,6 +228,15 @@
   </si>
   <si>
     <t>Thu Jul 09 23:00:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:35:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:35:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:36:25 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -634,7 +643,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s" s="1">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
@@ -651,7 +660,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s" s="1">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>5</v>
@@ -668,7 +677,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s" s="1">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>5</v>

--- a/KatalonData/RADTestData/JointFilerSSNmoreThan9Error.xlsx
+++ b/KatalonData/RADTestData/JointFilerSSNmoreThan9Error.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="67">
   <si>
     <t>Result</t>
   </si>
@@ -228,6 +228,15 @@
   </si>
   <si>
     <t>Thu Jul 09 23:00:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:13:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:14:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:14:15 EDT 2026</t>
   </si>
 </sst>
 </file>
@@ -634,7 +643,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s" s="1">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
@@ -651,7 +660,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s" s="1">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>5</v>
@@ -668,7 +677,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s" s="1">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>5</v>
